--- a/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/02_GJ_WP_2026-27/SL 2.0/Mahisagar.xlsx
+++ b/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/02_GJ_WP_2026-27/SL 2.0/Mahisagar.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026-27\ICS\2.0   PLANNING 2026-27\Kharif 2026-27\2.0\2.0 planning 2026-27\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Grv\Grv\05 GIT\01_masterRepo\06_Office_Related\01_NSO_work\06_SL_to_PIVOT_to_Compare_with_WP\02_GJ_WP_2026-27\SL 2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A5F0067-7C95-4498-BCBC-EF830B33B99F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97775BD6-BABF-464D-BB4B-5BBE70804C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="central 2.0" sheetId="1" r:id="rId1"/>
@@ -28,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="60">
   <si>
     <t xml:space="preserve">                               GUJARAT                                              STATEMENT NO. 4                                                  CENTRAL                                                                                      </t>
   </si>
@@ -214,6 +212,9 @@
   </si>
   <si>
     <t>Paddy(I)</t>
+  </si>
+  <si>
+    <t>ZZZ</t>
   </si>
 </sst>
 </file>
@@ -460,6 +461,39 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -469,40 +503,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -792,143 +793,144 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
-    </row>
-    <row r="2" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+    </row>
+    <row r="2" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21"/>
-      <c r="N2" s="21"/>
-      <c r="O2" s="21"/>
-      <c r="P2" s="21"/>
-    </row>
-    <row r="3" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19"/>
-      <c r="N3" s="19"/>
-      <c r="O3" s="19"/>
-      <c r="P3" s="19"/>
-    </row>
-    <row r="4" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="22" t="s">
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+    </row>
+    <row r="3" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+      <c r="O3" s="16"/>
+      <c r="P3" s="16"/>
+    </row>
+    <row r="4" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="26" t="s">
+      <c r="B4" s="18"/>
+      <c r="C4" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="23">
         <v>10</v>
       </c>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18">
+      <c r="E4" s="23"/>
+      <c r="F4" s="23">
         <v>10</v>
       </c>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18">
+      <c r="G4" s="23"/>
+      <c r="H4" s="23">
         <v>6</v>
       </c>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18">
-        <v>4</v>
-      </c>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18">
-        <v>4</v>
-      </c>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18">
-        <v>4</v>
-      </c>
-      <c r="O4" s="18"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23">
+        <v>4</v>
+      </c>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23">
+        <v>4</v>
+      </c>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23">
+        <v>4</v>
+      </c>
+      <c r="O4" s="23"/>
       <c r="P4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="24"/>
-      <c r="B5" s="25"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="20" t="s">
+    <row r="5" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="19"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20" t="s">
+      <c r="E5" s="29"/>
+      <c r="F5" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="G5" s="20"/>
+      <c r="G5" s="29"/>
       <c r="H5" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I5" s="4"/>
-      <c r="J5" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5" s="29"/>
-      <c r="L5" s="28" t="s">
+      <c r="J5" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="K5" s="25"/>
+      <c r="L5" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="M5" s="29"/>
-      <c r="N5" s="28" t="s">
+      <c r="M5" s="25"/>
+      <c r="N5" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="O5" s="29"/>
+      <c r="O5" s="25"/>
       <c r="P5" s="1">
         <f>SUM(D4:O4)</f>
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -976,7 +978,7 @@
       </c>
       <c r="P6" s="3"/>
     </row>
-    <row r="7" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>20</v>
       </c>
@@ -1019,7 +1021,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>22</v>
       </c>
@@ -1050,7 +1052,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>24</v>
       </c>
@@ -1081,7 +1083,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>26</v>
       </c>
@@ -1116,12 +1118,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+    <row r="11" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
       <c r="D11" s="4">
         <f>SUM(D7:D10)</f>
         <v>6</v>
@@ -1157,31 +1159,33 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
+    <row r="12" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="19"/>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19"/>
-      <c r="P12" s="19"/>
-    </row>
-    <row r="13" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="16"/>
+    </row>
+    <row r="13" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="3"/>
+      <c r="B13" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="C13" s="3" t="s">
         <v>28</v>
       </c>
@@ -1206,11 +1210,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="3"/>
+      <c r="B14" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="C14" s="3" t="s">
         <v>29</v>
       </c>
@@ -1235,11 +1241,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="3"/>
+      <c r="B15" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="C15" s="3" t="s">
         <v>30</v>
       </c>
@@ -1264,11 +1272,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="3"/>
+      <c r="B16" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="C16" s="3" t="s">
         <v>32</v>
       </c>
@@ -1293,11 +1303,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="3"/>
+      <c r="B17" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="C17" s="3" t="s">
         <v>34</v>
       </c>
@@ -1322,11 +1334,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="3"/>
+      <c r="B18" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="C18" s="3" t="s">
         <v>35</v>
       </c>
@@ -1351,11 +1365,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="3"/>
+      <c r="B19" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="C19" s="3" t="s">
         <v>36</v>
       </c>
@@ -1380,11 +1396,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B20" s="3"/>
+      <c r="B20" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="C20" s="12" t="s">
         <v>37</v>
       </c>
@@ -1409,11 +1427,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="3"/>
+      <c r="B21" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="C21" s="3" t="s">
         <v>38</v>
       </c>
@@ -1438,11 +1458,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="3"/>
+      <c r="B22" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="C22" s="12" t="s">
         <v>39</v>
       </c>
@@ -1467,11 +1489,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="3"/>
+      <c r="B23" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="C23" s="12" t="s">
         <v>40</v>
       </c>
@@ -1496,12 +1520,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="15" t="s">
+    <row r="24" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="17"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="28"/>
       <c r="D24" s="4">
         <f>SUM(D13:D23)</f>
         <v>4</v>
@@ -1537,12 +1561,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="15" t="s">
+    <row r="25" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="17"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="28"/>
       <c r="D25" s="4">
         <f>+D11+D24</f>
         <v>10</v>
@@ -1580,6 +1604,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A12:P12"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
     <mergeCell ref="A3:P3"/>
@@ -1594,12 +1624,6 @@
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="J5:K5"/>
     <mergeCell ref="L5:M5"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A12:P12"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1608,89 +1632,89 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AI20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:35" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
-    </row>
-    <row r="2" spans="1:35" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+    </row>
+    <row r="2" spans="1:35" ht="18" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21"/>
-      <c r="N2" s="21"/>
-      <c r="O2" s="21"/>
-      <c r="P2" s="21"/>
-    </row>
-    <row r="3" spans="1:35" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19"/>
-      <c r="N3" s="19"/>
-      <c r="O3" s="19"/>
-      <c r="P3" s="19"/>
-    </row>
-    <row r="4" spans="1:35" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="22" t="s">
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+    </row>
+    <row r="3" spans="1:35" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+      <c r="O3" s="16"/>
+      <c r="P3" s="16"/>
+    </row>
+    <row r="4" spans="1:35" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="26" t="s">
+      <c r="B4" s="18"/>
+      <c r="C4" s="21" t="s">
         <v>17</v>
       </c>
       <c r="D4" s="9">
         <v>4</v>
       </c>
       <c r="E4" s="10"/>
-      <c r="F4" s="18">
+      <c r="F4" s="23">
         <v>6</v>
       </c>
-      <c r="G4" s="18"/>
+      <c r="G4" s="23"/>
       <c r="H4" s="30">
         <v>4</v>
       </c>
@@ -1711,18 +1735,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="24"/>
-      <c r="B5" s="25"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="20" t="s">
+    <row r="5" spans="1:35" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="19"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="20"/>
-      <c r="F5" s="28" t="s">
+      <c r="E5" s="29"/>
+      <c r="F5" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="G5" s="29"/>
+      <c r="G5" s="25"/>
       <c r="H5" s="4" t="s">
         <v>18</v>
       </c>
@@ -1744,7 +1768,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -1792,7 +1816,7 @@
       </c>
       <c r="P6" s="3"/>
     </row>
-    <row r="7" spans="1:35" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>41</v>
       </c>
@@ -1826,7 +1850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>33</v>
       </c>
@@ -1860,7 +1884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>26</v>
       </c>
@@ -1906,12 +1930,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
+    <row r="10" spans="1:35" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
       <c r="D10" s="4">
         <f>SUM(D7:D9)</f>
         <v>4</v>
@@ -1947,31 +1971,33 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
+    <row r="11" spans="1:35" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="19"/>
-      <c r="P11" s="19"/>
-    </row>
-    <row r="12" spans="1:35" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="16"/>
+      <c r="P11" s="16"/>
+    </row>
+    <row r="12" spans="1:35" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="3"/>
+      <c r="B12" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="C12" s="3" t="s">
         <v>45</v>
       </c>
@@ -1996,11 +2022,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="3"/>
+      <c r="B13" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="C13" s="3" t="s">
         <v>46</v>
       </c>
@@ -2025,11 +2053,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="3"/>
+      <c r="B14" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="C14" s="3" t="s">
         <v>47</v>
       </c>
@@ -2054,11 +2084,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:35" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="3"/>
+      <c r="B15" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="C15" s="3" t="s">
         <v>48</v>
       </c>
@@ -2083,11 +2115,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="3"/>
+      <c r="B16" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="C16" s="3" t="s">
         <v>49</v>
       </c>
@@ -2112,11 +2146,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="3"/>
+      <c r="B17" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="C17" s="3" t="s">
         <v>50</v>
       </c>
@@ -2141,11 +2177,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="3"/>
+      <c r="B18" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="C18" s="3" t="s">
         <v>51</v>
       </c>
@@ -2170,12 +2208,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="15" t="s">
+    <row r="19" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="16"/>
-      <c r="C19" s="17"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="28"/>
       <c r="D19" s="4">
         <f>SUM(D12:D18)</f>
         <v>0</v>
@@ -2211,12 +2249,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
+    <row r="20" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="16"/>
-      <c r="C20" s="17"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="28"/>
       <c r="D20" s="4">
         <f>+D10+D19</f>
         <v>4</v>
@@ -2254,6 +2292,11 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A11:P11"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="D5:E5"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
     <mergeCell ref="A3:P3"/>
@@ -2265,11 +2308,6 @@
     <mergeCell ref="L4:M4"/>
     <mergeCell ref="N4:O4"/>
     <mergeCell ref="F5:G5"/>
-    <mergeCell ref="A11:P11"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="D5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
